--- a/exports/trend_1d/MPHASIS_full_report.xlsx
+++ b/exports/trend_1d/MPHASIS_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q62"/>
+  <dimension ref="A1:U62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>8.56</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42034</v>
+        <v>42037</v>
       </c>
       <c r="H2" t="n">
-        <v>293.6</v>
+        <v>279.8</v>
       </c>
       <c r="I2" t="n">
         <v>281.0928</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.49</v>
+        <v>-8.98</v>
       </c>
       <c r="L2" t="n">
-        <v>5.82</v>
+        <v>9.56</v>
       </c>
       <c r="M2" t="n">
         <v>1.13</v>
       </c>
       <c r="N2" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="O2" t="n">
         <v>-0.8100000000000001</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>12.78</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42051</v>
+        <v>42053</v>
       </c>
       <c r="H3" t="n">
-        <v>297.8</v>
+        <v>306.9</v>
       </c>
       <c r="I3" t="n">
         <v>304.8571951360253</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.43</v>
+        <v>-9.69</v>
       </c>
       <c r="L3" t="n">
         <v>11.51</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>16.64</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42381</v>
+        <v>42382</v>
       </c>
       <c r="H4" t="n">
-        <v>397.7</v>
+        <v>375.2</v>
       </c>
       <c r="I4" t="n">
         <v>383.634286987279</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K4" t="n">
-        <v>29.59</v>
+        <v>22.25</v>
       </c>
       <c r="L4" t="n">
         <v>6.68</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>223</v>
+        <v>224</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>12</v>
+      </c>
+      <c r="U4" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>18.42</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42445</v>
+        <v>42446</v>
       </c>
       <c r="H5" t="n">
-        <v>394.3</v>
+        <v>417.5</v>
       </c>
       <c r="I5" t="n">
         <v>409.100077757437</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.09</v>
+        <v>-11.27</v>
       </c>
       <c r="L5" t="n">
-        <v>8.130000000000001</v>
+        <v>13.75</v>
       </c>
       <c r="M5" t="n">
         <v>4.71</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>15.14</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42625</v>
+        <v>42627</v>
       </c>
       <c r="H6" t="n">
-        <v>448.4</v>
+        <v>441</v>
       </c>
       <c r="I6" t="n">
         <v>443.8213031360503</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="K6" t="n">
-        <v>7.4</v>
+        <v>5.63</v>
       </c>
       <c r="L6" t="n">
         <v>9.65</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>7</v>
+      </c>
+      <c r="U6" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>11.95</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42719</v>
+        <v>42720</v>
       </c>
       <c r="H7" t="n">
-        <v>471.6</v>
+        <v>487.4</v>
       </c>
       <c r="I7" t="n">
         <v>471.9498186072632</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.94</v>
+        <v>-10.52</v>
       </c>
       <c r="L7" t="n">
-        <v>9.369999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="M7" t="n">
         <v>1.6</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>11.13</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42825</v>
+        <v>42828</v>
       </c>
       <c r="H8" t="n">
-        <v>501.2</v>
+        <v>494.9</v>
       </c>
       <c r="I8" t="n">
         <v>497.488669184823</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K8" t="n">
-        <v>2.83</v>
+        <v>1.54</v>
       </c>
       <c r="L8" t="n">
         <v>9.68</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>6.36</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42857</v>
+        <v>42858</v>
       </c>
       <c r="H9" t="n">
-        <v>484.8</v>
+        <v>491</v>
       </c>
       <c r="I9" t="n">
         <v>489.5731690193705</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K9" t="n">
-        <v>2.04</v>
+        <v>0.79</v>
       </c>
       <c r="L9" t="n">
         <v>1.19</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.12</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43369</v>
+        <v>43370</v>
       </c>
       <c r="H10" t="n">
-        <v>1074.6</v>
+        <v>1055.1</v>
       </c>
       <c r="I10" t="n">
         <v>1062.95889298909</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K10" t="n">
-        <v>118.86</v>
+        <v>114.89</v>
       </c>
       <c r="L10" t="n">
         <v>8.49</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>349</v>
+        <v>350</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>17</v>
+      </c>
+      <c r="U10" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>8.34</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43493</v>
+        <v>43494</v>
       </c>
       <c r="H11" t="n">
-        <v>845.9</v>
+        <v>876.3</v>
       </c>
       <c r="I11" t="n">
         <v>863.6779558741756</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K11" t="n">
-        <v>19.83</v>
+        <v>16.95</v>
       </c>
       <c r="L11" t="n">
         <v>2.49</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>12.61</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43537</v>
+        <v>43538</v>
       </c>
       <c r="H12" t="n">
-        <v>879.1</v>
+        <v>862.7</v>
       </c>
       <c r="I12" t="n">
         <v>866.0659892142473</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K12" t="n">
-        <v>0.32</v>
+        <v>-1.55</v>
       </c>
       <c r="L12" t="n">
         <v>4.11</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>10.22</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43643</v>
+        <v>43644</v>
       </c>
       <c r="H13" t="n">
-        <v>893.5</v>
+        <v>906.2</v>
       </c>
       <c r="I13" t="n">
         <v>903.8111740364823</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.57</v>
+        <v>-5.04</v>
       </c>
       <c r="L13" t="n">
-        <v>6.51</v>
+        <v>6.57</v>
       </c>
       <c r="M13" t="n">
         <v>1.22</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>9.57</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43669</v>
+        <v>43670</v>
       </c>
       <c r="H14" t="n">
-        <v>821.9</v>
+        <v>820.2</v>
       </c>
       <c r="I14" t="n">
         <v>820.7476940873502</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K14" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.49</v>
       </c>
       <c r="L14" t="n">
         <v>10.22</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>7.99</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43699</v>
+        <v>43700</v>
       </c>
       <c r="H15" t="n">
-        <v>868.7</v>
+        <v>885.9</v>
       </c>
       <c r="I15" t="n">
         <v>885.7028110403638</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.91</v>
+        <v>-8.01</v>
       </c>
       <c r="L15" t="n">
         <v>8.74</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>8.49</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43745</v>
+        <v>43747</v>
       </c>
       <c r="H16" t="n">
-        <v>857.8</v>
+        <v>834.9</v>
       </c>
       <c r="I16" t="n">
         <v>839.1282209165628</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.17</v>
+        <v>-5.76</v>
       </c>
       <c r="L16" t="n">
-        <v>5.22</v>
+        <v>6.32</v>
       </c>
       <c r="M16" t="n">
         <v>0.47</v>
       </c>
       <c r="N16" t="n">
-        <v>2.16</v>
+        <v>2.67</v>
       </c>
       <c r="O16" t="n">
         <v>1.98</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>8.68</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43829</v>
+        <v>43830</v>
       </c>
       <c r="H17" t="n">
-        <v>814.6</v>
+        <v>828.1</v>
       </c>
       <c r="I17" t="n">
         <v>819.8163943909121</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K17" t="n">
-        <v>2.43</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L17" t="n">
         <v>3.15</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43886</v>
+        <v>43887</v>
       </c>
       <c r="H18" t="n">
-        <v>791.9</v>
+        <v>760.9</v>
       </c>
       <c r="I18" t="n">
         <v>777.3949906995337</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.37</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>6.26</v>
+        <v>9.49</v>
       </c>
       <c r="M18" t="n">
         <v>1.63</v>
       </c>
       <c r="N18" t="n">
-        <v>3.44</v>
+        <v>3.91</v>
       </c>
       <c r="O18" t="n">
         <v>1.66</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>10.9</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43962</v>
+        <v>43963</v>
       </c>
       <c r="H19" t="n">
-        <v>690</v>
+        <v>717.5</v>
       </c>
       <c r="I19" t="n">
         <v>715.2259233830076</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K19" t="n">
-        <v>9.32</v>
+        <v>5.7</v>
       </c>
       <c r="L19" t="n">
         <v>6.14</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>19.73</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44469</v>
+        <v>44470</v>
       </c>
       <c r="H20" t="n">
-        <v>2911.6</v>
+        <v>2836.9</v>
       </c>
       <c r="I20" t="n">
         <v>2857.464118298288</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K20" t="n">
-        <v>305.8</v>
+        <v>295.39</v>
       </c>
       <c r="L20" t="n">
         <v>7.12</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>349</v>
+        <v>350</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>18</v>
+      </c>
+      <c r="U20" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>15</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44487</v>
+        <v>44488</v>
       </c>
       <c r="H21" t="n">
-        <v>3152.5</v>
+        <v>3333.7</v>
       </c>
       <c r="I21" t="n">
         <v>3249.28097180744</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K21" t="n">
-        <v>-11.12</v>
+        <v>-17.51</v>
       </c>
       <c r="L21" t="n">
-        <v>14.43</v>
+        <v>21.32</v>
       </c>
       <c r="M21" t="n">
         <v>3.84</v>
       </c>
       <c r="N21" t="n">
-        <v>4.43</v>
+        <v>5.75</v>
       </c>
       <c r="O21" t="n">
         <v>-2.57</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>14.35</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H22" t="n">
-        <v>3061.7</v>
+        <v>2868.4</v>
       </c>
       <c r="I22" t="n">
         <v>2914.328807468203</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K22" t="n">
-        <v>-8.16</v>
+        <v>-13.96</v>
       </c>
       <c r="L22" t="n">
-        <v>13.22</v>
+        <v>14.82</v>
       </c>
       <c r="M22" t="n">
         <v>5.88</v>
       </c>
       <c r="N22" t="n">
-        <v>4.24</v>
+        <v>6.31</v>
       </c>
       <c r="O22" t="n">
         <v>5.75</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>15.94</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44561</v>
+        <v>44564</v>
       </c>
       <c r="H23" t="n">
-        <v>3190.7</v>
+        <v>3215.5</v>
       </c>
       <c r="I23" t="n">
         <v>3194.335539305035</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K23" t="n">
-        <v>-11.24</v>
+        <v>-12.1</v>
       </c>
       <c r="L23" t="n">
-        <v>11.99</v>
+        <v>13.98</v>
       </c>
       <c r="M23" t="n">
         <v>2.95</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>8.83</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44579</v>
+        <v>44580</v>
       </c>
       <c r="H24" t="n">
-        <v>3004.4</v>
+        <v>2896.2</v>
       </c>
       <c r="I24" t="n">
         <v>2931.681916064075</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K24" t="n">
-        <v>-6.57</v>
+        <v>-9.93</v>
       </c>
       <c r="L24" t="n">
-        <v>7.33</v>
+        <v>10.83</v>
       </c>
       <c r="M24" t="n">
         <v>0.48</v>
       </c>
       <c r="N24" t="n">
-        <v>2.57</v>
+        <v>3.6</v>
       </c>
       <c r="O24" t="n">
         <v>0.78</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>11.44</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44631</v>
+        <v>44634</v>
       </c>
       <c r="H25" t="n">
-        <v>3084.9</v>
+        <v>3110.9</v>
       </c>
       <c r="I25" t="n">
         <v>3098.718479535993</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K25" t="n">
-        <v>-6.52</v>
+        <v>-7.41</v>
       </c>
       <c r="L25" t="n">
-        <v>6.98</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M25" t="n">
         <v>2.69</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,25 +2213,25 @@
         <v>10.59</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44662</v>
+        <v>44663</v>
       </c>
       <c r="H26" t="n">
-        <v>2935.3</v>
+        <v>2866.6</v>
       </c>
       <c r="I26" t="n">
         <v>2898.653218592998</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K26" t="n">
-        <v>-5.64</v>
+        <v>-7.85</v>
       </c>
       <c r="L26" t="n">
         <v>8.9</v>
       </c>
       <c r="M26" t="n">
-        <v>0.37</v>
+        <v>0.64</v>
       </c>
       <c r="N26" t="n">
         <v>3.87</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>10.07</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44776</v>
+        <v>44777</v>
       </c>
       <c r="H27" t="n">
-        <v>2162.6</v>
+        <v>2211.8</v>
       </c>
       <c r="I27" t="n">
         <v>2190.760742924994</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K27" t="n">
-        <v>24.56</v>
+        <v>22.84</v>
       </c>
       <c r="L27" t="n">
         <v>2.12</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>10.69</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44797</v>
+        <v>44798</v>
       </c>
       <c r="H28" t="n">
-        <v>2067.6</v>
+        <v>2041.4</v>
       </c>
       <c r="I28" t="n">
         <v>2048.686496624992</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K28" t="n">
-        <v>-6.52</v>
+        <v>-7.7</v>
       </c>
       <c r="L28" t="n">
-        <v>6.97</v>
+        <v>7.92</v>
       </c>
       <c r="M28" t="n">
         <v>1.58</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>11.49</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44895</v>
+        <v>44896</v>
       </c>
       <c r="H29" t="n">
-        <v>1873.6</v>
+        <v>1986.2</v>
       </c>
       <c r="I29" t="n">
         <v>1923.619146472518</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K29" t="n">
-        <v>8.220000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="L29" t="n">
         <v>2.43</v>
@@ -2094,7 +2441,7 @@
         <v>2.89</v>
       </c>
       <c r="N29" t="n">
-        <v>5.26</v>
+        <v>6.01</v>
       </c>
       <c r="O29" t="n">
         <v>-1.27</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2130,25 +2489,25 @@
         <v>10.38</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44909</v>
+        <v>44910</v>
       </c>
       <c r="H30" t="n">
-        <v>1857.9</v>
+        <v>1821.2</v>
       </c>
       <c r="I30" t="n">
         <v>1841.975714161394</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K30" t="n">
-        <v>-6.46</v>
+        <v>-8.31</v>
       </c>
       <c r="L30" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>0.53</v>
+        <v>0.66</v>
       </c>
       <c r="N30" t="n">
         <v>4.11</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>9.56</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44949</v>
+        <v>44950</v>
       </c>
       <c r="H31" t="n">
-        <v>1913.2</v>
+        <v>1969</v>
       </c>
       <c r="I31" t="n">
         <v>1922.86136321439</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K31" t="n">
-        <v>-5.05</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>5.73</v>
+        <v>9.5</v>
       </c>
       <c r="M31" t="n">
         <v>1.45</v>
       </c>
       <c r="N31" t="n">
-        <v>2.19</v>
+        <v>2.92</v>
       </c>
       <c r="O31" t="n">
         <v>-1.98</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44981</v>
+        <v>44984</v>
       </c>
       <c r="H32" t="n">
-        <v>2046.1</v>
+        <v>1895.2</v>
       </c>
       <c r="I32" t="n">
         <v>1927.864195008495</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K32" t="n">
-        <v>3.92</v>
+        <v>-3.75</v>
       </c>
       <c r="L32" t="n">
-        <v>3.64</v>
+        <v>4.62</v>
       </c>
       <c r="M32" t="n">
-        <v>1.1</v>
+        <v>2.23</v>
       </c>
       <c r="N32" t="n">
-        <v>2.29</v>
+        <v>7.38</v>
       </c>
       <c r="O32" t="n">
         <v>2.92</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>12.45</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45056</v>
+        <v>45057</v>
       </c>
       <c r="H33" t="n">
-        <v>1728.9</v>
+        <v>1735.1</v>
       </c>
       <c r="I33" t="n">
         <v>1733.104665851955</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K33" t="n">
-        <v>8.77</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="L33" t="n">
         <v>5.79</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>7.12</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45085</v>
+        <v>45086</v>
       </c>
       <c r="H34" t="n">
-        <v>1727.1</v>
+        <v>1717</v>
       </c>
       <c r="I34" t="n">
         <v>1722.444535538302</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.46</v>
+        <v>-1.04</v>
       </c>
       <c r="L34" t="n">
         <v>1.8</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45120</v>
+        <v>45121</v>
       </c>
       <c r="H35" t="n">
-        <v>1782.8</v>
+        <v>1923.5</v>
       </c>
       <c r="I35" t="n">
         <v>1790.536689646141</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K35" t="n">
-        <v>-3.83</v>
+        <v>-12.03</v>
       </c>
       <c r="L35" t="n">
-        <v>5.65</v>
+        <v>12.55</v>
       </c>
       <c r="M35" t="n">
         <v>1.45</v>
       </c>
       <c r="N35" t="n">
-        <v>2.57</v>
+        <v>7.89</v>
       </c>
       <c r="O35" t="n">
         <v>-0.58</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>10.5</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45215</v>
+        <v>45216</v>
       </c>
       <c r="H36" t="n">
-        <v>2200.4</v>
+        <v>2134.8</v>
       </c>
       <c r="I36" t="n">
         <v>2165.190204374116</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K36" t="n">
-        <v>14.4</v>
+        <v>10.99</v>
       </c>
       <c r="L36" t="n">
         <v>6.68</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>10.72</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45245</v>
+        <v>45246</v>
       </c>
       <c r="H37" t="n">
-        <v>2114</v>
+        <v>2206.2</v>
       </c>
       <c r="I37" t="n">
         <v>2164.302225788839</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K37" t="n">
-        <v>0.97</v>
+        <v>-3.34</v>
       </c>
       <c r="L37" t="n">
-        <v>3.63</v>
+        <v>4.61</v>
       </c>
       <c r="M37" t="n">
         <v>3.13</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>10.12</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45308</v>
+        <v>45309</v>
       </c>
       <c r="H38" t="n">
-        <v>2455.8</v>
+        <v>2348</v>
       </c>
       <c r="I38" t="n">
         <v>2357.7109659361</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K38" t="n">
-        <v>11.31</v>
+        <v>6.43</v>
       </c>
       <c r="L38" t="n">
         <v>4.91</v>
@@ -2607,7 +3062,7 @@
         <v>1.91</v>
       </c>
       <c r="N38" t="n">
-        <v>3.62</v>
+        <v>4.39</v>
       </c>
       <c r="O38" t="n">
         <v>4.36</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>12.8</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="H39" t="n">
-        <v>2533.7</v>
+        <v>2622.8</v>
       </c>
       <c r="I39" t="n">
         <v>2598.450789088828</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K39" t="n">
-        <v>-7.91</v>
+        <v>-11.7</v>
       </c>
       <c r="L39" t="n">
-        <v>8.58</v>
+        <v>12.39</v>
       </c>
       <c r="M39" t="n">
         <v>1.17</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>12.18</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="H40" t="n">
-        <v>2356.6</v>
+        <v>2327.7</v>
       </c>
       <c r="I40" t="n">
         <v>2342.311132099328</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K40" t="n">
-        <v>-10.15</v>
+        <v>-11.25</v>
       </c>
       <c r="L40" t="n">
         <v>12.41</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>11.26</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45436</v>
+        <v>45439</v>
       </c>
       <c r="H41" t="n">
-        <v>2230.4</v>
+        <v>2278.3</v>
       </c>
       <c r="I41" t="n">
         <v>2251.075633453599</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K41" t="n">
-        <v>4.18</v>
+        <v>2.12</v>
       </c>
       <c r="L41" t="n">
         <v>2.62</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>8.19</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="H42" t="n">
-        <v>2532.4</v>
+        <v>2519.7</v>
       </c>
       <c r="I42" t="n">
         <v>2528.724797036565</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K42" t="n">
-        <v>11.15</v>
+        <v>10.6</v>
       </c>
       <c r="L42" t="n">
         <v>10.65</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>13.54</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45523</v>
+        <v>45524</v>
       </c>
       <c r="H43" t="n">
-        <v>2843.2</v>
+        <v>2873</v>
       </c>
       <c r="I43" t="n">
         <v>2850.598544837227</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K43" t="n">
-        <v>-12.84</v>
+        <v>-14.02</v>
       </c>
       <c r="L43" t="n">
-        <v>13.41</v>
+        <v>15.09</v>
       </c>
       <c r="M43" t="n">
         <v>2.25</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>9.44</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45568</v>
+        <v>45569</v>
       </c>
       <c r="H44" t="n">
-        <v>2789</v>
+        <v>2717.9</v>
       </c>
       <c r="I44" t="n">
         <v>2777.435156459906</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.92</v>
+        <v>-5.4</v>
       </c>
       <c r="L44" t="n">
-        <v>3.44</v>
+        <v>5.73</v>
       </c>
       <c r="M44" t="n">
         <v>1.99</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>11.32</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45625</v>
+        <v>45628</v>
       </c>
       <c r="H45" t="n">
-        <v>2840.2</v>
+        <v>2912.1</v>
       </c>
       <c r="I45" t="n">
         <v>2883.555136189079</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K45" t="n">
-        <v>-4.5</v>
+        <v>-7.15</v>
       </c>
       <c r="L45" t="n">
         <v>10.47</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>9.68</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H46" t="n">
-        <v>2976.2</v>
+        <v>2817.3</v>
       </c>
       <c r="I46" t="n">
         <v>2853.501646762909</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K46" t="n">
-        <v>2.2</v>
+        <v>-3.26</v>
       </c>
       <c r="L46" t="n">
-        <v>3.16</v>
+        <v>3.76</v>
       </c>
       <c r="M46" t="n">
         <v>3</v>
       </c>
       <c r="N46" t="n">
-        <v>1.87</v>
+        <v>5.34</v>
       </c>
       <c r="O46" t="n">
         <v>2.53</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>13.67</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H47" t="n">
-        <v>2320.1</v>
+        <v>2370.7</v>
       </c>
       <c r="I47" t="n">
         <v>2359.274638002362</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K47" t="n">
-        <v>17.65</v>
+        <v>15.85</v>
       </c>
       <c r="L47" t="n">
         <v>8.35</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>12.98</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45750</v>
+        <v>45751</v>
       </c>
       <c r="H48" t="n">
-        <v>2266.7</v>
+        <v>2128.4</v>
       </c>
       <c r="I48" t="n">
         <v>2153.837885434848</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.39</v>
+        <v>-10.22</v>
       </c>
       <c r="L48" t="n">
-        <v>5.19</v>
+        <v>10.59</v>
       </c>
       <c r="M48" t="n">
         <v>3.93</v>
       </c>
       <c r="N48" t="n">
-        <v>4.06</v>
+        <v>6.1</v>
       </c>
       <c r="O48" t="n">
         <v>2.18</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>16.04</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45768</v>
+        <v>45769</v>
       </c>
       <c r="H49" t="n">
-        <v>2273.2</v>
+        <v>2293.2</v>
       </c>
       <c r="I49" t="n">
         <v>2292.196997223957</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K49" t="n">
-        <v>-6.8</v>
+        <v>-7.74</v>
       </c>
       <c r="L49" t="n">
-        <v>8.49</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="M49" t="n">
         <v>4.84</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>13.48</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45861</v>
+        <v>45862</v>
       </c>
       <c r="H50" t="n">
-        <v>2665</v>
+        <v>2584.2</v>
       </c>
       <c r="I50" t="n">
         <v>2629.471855378291</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K50" t="n">
-        <v>16.21</v>
+        <v>12.69</v>
       </c>
       <c r="L50" t="n">
         <v>3.78</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>9.07</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45891</v>
+        <v>45894</v>
       </c>
       <c r="H51" t="n">
-        <v>2774.2</v>
+        <v>2841.5</v>
       </c>
       <c r="I51" t="n">
         <v>2818.512606055906</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K51" t="n">
-        <v>-7.35</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>8.82</v>
+        <v>11.84</v>
       </c>
       <c r="M51" t="n">
         <v>2.48</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>7.54</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="H52" t="n">
-        <v>2777.9</v>
+        <v>2694.4</v>
       </c>
       <c r="I52" t="n">
         <v>2709.536996620287</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K52" t="n">
-        <v>-2.24</v>
+        <v>-5.18</v>
       </c>
       <c r="L52" t="n">
-        <v>5.38</v>
+        <v>5.63</v>
       </c>
       <c r="M52" t="n">
         <v>2.49</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>10.13</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="H53" t="n">
-        <v>2786.3</v>
+        <v>2832.5</v>
       </c>
       <c r="I53" t="n">
         <v>2820.088017038426</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.41</v>
+        <v>-5.13</v>
       </c>
       <c r="L53" t="n">
         <v>7.03</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>6.26</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="H54" t="n">
-        <v>2736.7</v>
+        <v>2680.9</v>
       </c>
       <c r="I54" t="n">
         <v>2694.637654224249</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.38</v>
+        <v>-5.35</v>
       </c>
       <c r="L54" t="n">
         <v>6.44</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>11.59</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="H55" t="n">
-        <v>2176.8</v>
+        <v>2267.3</v>
       </c>
       <c r="I55" t="n">
         <v>2226.698767755272</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K55" t="n">
-        <v>18.8</v>
+        <v>15.43</v>
       </c>
       <c r="L55" t="n">
         <v>8.07</v>
@@ -3576,7 +4235,7 @@
         <v>7.73</v>
       </c>
       <c r="N55" t="n">
-        <v>4.07</v>
+        <v>4.16</v>
       </c>
       <c r="O55" t="n">
         <v>-2.04</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>13.75</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="H56" t="n">
-        <v>2217.5</v>
+        <v>2119</v>
       </c>
       <c r="I56" t="n">
         <v>2129.017061738695</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K56" t="n">
-        <v>-2.2</v>
+        <v>-6.54</v>
       </c>
       <c r="L56" t="n">
-        <v>5.2</v>
+        <v>8.51</v>
       </c>
       <c r="M56" t="n">
         <v>1.36</v>
       </c>
       <c r="N56" t="n">
-        <v>3.64</v>
+        <v>4.44</v>
       </c>
       <c r="O56" t="n">
         <v>4.16</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>13.89</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="H57" t="n">
-        <v>2250.2</v>
+        <v>2325.4</v>
       </c>
       <c r="I57" t="n">
         <v>2258.713042355256</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K57" t="n">
-        <v>-6.19</v>
+        <v>-9.74</v>
       </c>
       <c r="L57" t="n">
-        <v>9.06</v>
+        <v>11.7</v>
       </c>
       <c r="M57" t="n">
         <v>3</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>10.27</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="H58" t="n">
-        <v>2105.2</v>
+        <v>2071.3</v>
       </c>
       <c r="I58" t="n">
         <v>2086.552134775431</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K58" t="n">
-        <v>-9.470000000000001</v>
+        <v>-10.93</v>
       </c>
       <c r="L58" t="n">
-        <v>9.960000000000001</v>
+        <v>11.17</v>
       </c>
       <c r="M58" t="n">
         <v>6.93</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>11.18</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="H59" t="n">
-        <v>2247</v>
+        <v>2312.6</v>
       </c>
       <c r="I59" t="n">
         <v>2302.931997306634</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K59" t="n">
-        <v>-8.48</v>
+        <v>-11.65</v>
       </c>
       <c r="L59" t="n">
-        <v>9.6</v>
+        <v>12.99</v>
       </c>
       <c r="M59" t="n">
         <v>1.5</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>10.21</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="H60" t="n">
-        <v>2307.5</v>
+        <v>2291.7</v>
       </c>
       <c r="I60" t="n">
         <v>2307.149210334134</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.22</v>
+        <v>-0.9</v>
       </c>
       <c r="L60" t="n">
         <v>5.21</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>9.359999999999999</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="H61" t="n">
-        <v>2353.5</v>
+        <v>2466.3</v>
       </c>
       <c r="I61" t="n">
         <v>2378.036799394515</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.7</v>
+        <v>-7.62</v>
       </c>
       <c r="L61" t="n">
-        <v>7.39</v>
+        <v>7.67</v>
       </c>
       <c r="M61" t="n">
         <v>2.53</v>
       </c>
       <c r="N61" t="n">
-        <v>4.45</v>
+        <v>4.79</v>
       </c>
       <c r="O61" t="n">
         <v>-0.68</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3978,6 +4721,14 @@
       <c r="Q62" t="n">
         <v>11</v>
       </c>
+      <c r="R62" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8936,7 +9687,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70.09999999999999</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="6">
@@ -8946,7 +9697,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -8956,7 +9707,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="8">
@@ -8966,7 +9717,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -8976,7 +9727,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75.8</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="10">
@@ -8986,7 +9737,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>105.8</v>
+        <v>108.6</v>
       </c>
     </row>
     <row r="11">
@@ -8996,7 +9747,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -9006,7 +9757,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -9016,7 +9767,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>38.3</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="14">
@@ -9026,7 +9777,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7.08</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="15">
@@ -9036,7 +9787,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14.46</v>
+        <v>11.16</v>
       </c>
     </row>
     <row r="16">
@@ -9046,7 +9797,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.3</v>
+        <v>-3.27</v>
       </c>
     </row>
     <row r="17">
@@ -9056,7 +9807,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>305.8</v>
+        <v>295.39</v>
       </c>
     </row>
     <row r="18">
@@ -9066,7 +9817,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>38.3</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="19">
@@ -9076,7 +9827,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.07</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -9086,7 +9837,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.98</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="21">
@@ -9096,7 +9847,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.43</v>
+        <v>21.32</v>
       </c>
     </row>
     <row r="22">
@@ -9106,7 +9857,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23">
@@ -9116,7 +9867,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
@@ -9126,7 +9877,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="25">
@@ -9146,7 +9897,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.48</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="27">
@@ -9166,7 +9917,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29">
